--- a/LLD templateV1.0.xlsx
+++ b/LLD templateV1.0.xlsx
@@ -1247,7 +1247,7 @@
       </c>
       <c r="L1" s="18" t="inlineStr">
         <is>
-          <t>SITE INFORMATION</t>
+          <t>SiteCode</t>
         </is>
       </c>
       <c r="M1" s="18" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="K1" s="20" t="inlineStr">
         <is>
-          <t>SITE INFORMATION</t>
+          <t>SiteCode</t>
         </is>
       </c>
       <c r="L1" s="20" t="inlineStr">
